--- a/Tableau.xlsx
+++ b/Tableau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/maelys_houssein_wppmedia_com/Documents/Documents/portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{FB2C839A-B830-486F-9CA2-B23C907ECE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B12BCF-2ACF-4C6F-B423-5136680569D2}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{FB2C839A-B830-486F-9CA2-B23C907ECE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70BA6F37-D97C-428F-965A-361412CD129D}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t xml:space="preserve"> SISR</t>
   </si>
   <si>
-    <t>AP 5.1 ValorElec - Intégration Active Directory et automatisation des comptes utilisateurs</t>
-  </si>
-  <si>
     <t>ValorElec - Mise en place d’un serveur de fichiers centralisé avec TrueNAS et iSCSI</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
   </si>
   <si>
     <t>Étude et déploiement d’une racine DFS pour la gestion multisite</t>
-  </si>
-  <si>
-    <t>Automatisation des scripts PowerShell pour la gestion des droits et déploiement logiciel</t>
   </si>
   <si>
     <t>N° candidat : 02148773677</t>
@@ -162,6 +156,14 @@
   </si>
   <si>
     <t>ss</t>
+  </si>
+  <si>
+    <t>AP 5.1 ValorElec - Intégration Active Directory et automatisation des comptes
+ utilisateurs</t>
+  </si>
+  <si>
+    <t>Automatisation des scripts PowerShell pour la gestion des droits et déploiement 
+logiciel</t>
   </si>
 </sst>
 </file>
@@ -593,16 +595,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -627,20 +643,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -658,6 +662,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -961,56 +969,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1022,10 +1030,10 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="39" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1048,8 +1056,8 @@
       </c>
     </row>
     <row r="6" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="36"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="8" t="s">
         <v>9</v>
       </c>
@@ -1105,16 +1113,16 @@
       <c r="AQ6"/>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="31"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1198,9 +1206,11 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="B9" s="41">
+        <v>46098</v>
+      </c>
       <c r="C9" s="23"/>
       <c r="D9" s="24"/>
       <c r="E9" s="18"/>
@@ -1245,9 +1255,11 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="B10" s="41">
+        <v>46108</v>
+      </c>
       <c r="C10" s="23"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -1292,9 +1304,11 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="B11" s="41">
+        <v>46107</v>
+      </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="18"/>
@@ -1339,9 +1353,11 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10"/>
+        <v>27</v>
+      </c>
+      <c r="B12" s="41">
+        <v>46104</v>
+      </c>
       <c r="C12" s="23"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -1385,10 +1401,12 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10"/>
+      <c r="A13" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="41">
+        <v>46103</v>
+      </c>
       <c r="C13" s="18"/>
       <c r="D13" s="23"/>
       <c r="E13" s="18"/>
@@ -1433,7 +1451,9 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
-      <c r="B14" s="10"/>
+      <c r="B14" s="41">
+        <v>46114</v>
+      </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
@@ -1478,7 +1498,9 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
+      <c r="B15" s="41">
+        <v>46114</v>
+      </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
@@ -1523,7 +1545,9 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
+      <c r="B16" s="41">
+        <v>46114</v>
+      </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -1568,7 +1592,9 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
+      <c r="B17" s="41">
+        <v>46114</v>
+      </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -1612,16 +1638,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="34"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1659,10 +1685,12 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="10"/>
+      <c r="A19" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="41">
+        <v>46142</v>
+      </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="18"/>
@@ -1706,10 +1734,12 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="10"/>
+      <c r="A20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="41">
+        <v>46106</v>
+      </c>
       <c r="C20" s="23"/>
       <c r="D20" s="24"/>
       <c r="E20" s="18"/>
@@ -1753,10 +1783,12 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="10"/>
+      <c r="A21" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="41">
+        <v>46100</v>
+      </c>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
       <c r="E21" s="18"/>
@@ -1800,10 +1832,12 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="10"/>
+      <c r="A22" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="41">
+        <v>46114</v>
+      </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
       <c r="E22" s="18"/>
@@ -2027,16 +2061,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2074,10 +2108,12 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="10"/>
+      <c r="A28" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="41">
+        <v>45800</v>
+      </c>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
       <c r="E28" s="18"/>
@@ -2121,10 +2157,12 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="10"/>
+      <c r="A29" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="41">
+        <v>45839</v>
+      </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="23"/>
@@ -2168,8 +2206,8 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
-        <v>37</v>
+      <c r="A30" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="18"/>
@@ -2532,17 +2570,17 @@
     <row r="82" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
